--- a/grupos/3ALCM - Estadisticos 20231.xlsx
+++ b/grupos/3ALCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="90">
   <si>
     <t>Materia</t>
   </si>
@@ -218,18 +218,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -248,7 +248,10 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>MENDOZA</t>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
   </si>
   <si>
     <t>ROJAS</t>
@@ -257,16 +260,13 @@
     <t>TEPOLE</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
   </si>
   <si>
     <t>SOTO</t>
@@ -275,34 +275,19 @@
     <t>GIL</t>
   </si>
   <si>
-    <t>ESPIRITU</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>ANETTE</t>
   </si>
   <si>
-    <t>VALERIA</t>
+    <t>BARUCH BOSET</t>
+  </si>
+  <si>
+    <t>ILEANA</t>
   </si>
   <si>
     <t>ANDRES</t>
   </si>
   <si>
     <t>JESUS</t>
-  </si>
-  <si>
-    <t>MARCO</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
   </si>
 </sst>
 </file>
@@ -813,19 +798,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -849,7 +834,7 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -858,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -890,19 +875,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -926,13 +911,13 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -967,19 +952,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1006,7 +991,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1044,19 +1029,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1080,19 +1065,19 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
+        <v>7</v>
+      </c>
+      <c r="W7">
         <v>6</v>
       </c>
-      <c r="W7">
-        <v>5</v>
-      </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1121,19 +1106,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1163,13 +1148,13 @@
         <v>7</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1198,19 +1183,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1237,16 +1222,16 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1275,19 +1260,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1311,19 +1296,19 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1352,19 +1337,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1388,7 +1373,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1400,7 +1385,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1429,19 +1414,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1465,13 +1450,13 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1506,19 +1491,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1542,13 +1527,13 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1583,19 +1568,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1619,10 +1604,10 @@
         <v>9</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1660,19 +1645,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1696,13 +1681,13 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>8</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1737,19 +1722,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1776,16 +1761,16 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1814,19 +1799,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1850,19 +1835,19 @@
         <v>9</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1882,7 +1867,7 @@
         <v>8</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18">
         <v>8</v>
@@ -1891,19 +1876,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1927,16 +1912,16 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>8</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>8</v>
@@ -1968,19 +1953,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2010,13 +1995,13 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2045,19 +2030,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2081,16 +2066,16 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2122,19 +2107,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2158,7 +2143,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>5</v>
@@ -2170,7 +2155,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2199,19 +2184,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2235,16 +2220,16 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2276,19 +2261,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2312,7 +2297,7 @@
         <v>5</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V23">
         <v>5</v>
@@ -2353,19 +2338,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2389,19 +2374,19 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>9</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2430,19 +2415,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2466,13 +2451,13 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2507,19 +2492,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2543,16 +2528,16 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2584,19 +2569,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2620,13 +2605,13 @@
         <v>9</v>
       </c>
       <c r="U27">
+        <v>5</v>
+      </c>
+      <c r="V27">
         <v>6</v>
       </c>
-      <c r="V27">
-        <v>7</v>
-      </c>
       <c r="W27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>5</v>
@@ -2661,19 +2646,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2700,10 +2685,10 @@
         <v>9</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2738,19 +2723,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2774,19 +2759,19 @@
         <v>9</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>8</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2815,19 +2800,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2854,16 +2839,16 @@
         <v>5</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>5</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2892,19 +2877,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2928,19 +2913,19 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2969,19 +2954,19 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3005,19 +2990,19 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3046,19 +3031,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3082,13 +3067,13 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>9</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3123,19 +3108,19 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3162,7 +3147,7 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
         <v>8</v>
@@ -3171,7 +3156,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3200,19 +3185,19 @@
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3236,13 +3221,13 @@
         <v>9</v>
       </c>
       <c r="U35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>7</v>
       </c>
       <c r="W35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X35">
         <v>5</v>
@@ -3277,19 +3262,19 @@
         <v>-1</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3322,7 +3307,7 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3354,19 +3339,19 @@
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3390,13 +3375,13 @@
         <v>7</v>
       </c>
       <c r="U37">
+        <v>7</v>
+      </c>
+      <c r="V37">
+        <v>8</v>
+      </c>
+      <c r="W37">
         <v>6</v>
-      </c>
-      <c r="V37">
-        <v>9</v>
-      </c>
-      <c r="W37">
-        <v>5</v>
       </c>
       <c r="X37">
         <v>7</v>
@@ -3431,19 +3416,19 @@
         <v>-1</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3508,19 +3493,19 @@
         <v>-1</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3544,13 +3529,13 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V39">
         <v>9</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -3585,19 +3570,19 @@
         <v>-1</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3624,10 +3609,10 @@
         <v>8</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>9</v>
@@ -3662,19 +3647,19 @@
         <v>-1</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3704,7 +3689,7 @@
         <v>10</v>
       </c>
       <c r="W41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X41">
         <v>10</v>
@@ -3739,19 +3724,19 @@
         <v>-1</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3775,13 +3760,13 @@
         <v>9</v>
       </c>
       <c r="U42">
+        <v>7</v>
+      </c>
+      <c r="V42">
+        <v>7</v>
+      </c>
+      <c r="W42">
         <v>6</v>
-      </c>
-      <c r="V42">
-        <v>6</v>
-      </c>
-      <c r="W42">
-        <v>5</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -3816,19 +3801,19 @@
         <v>-1</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -3852,19 +3837,19 @@
         <v>8</v>
       </c>
       <c r="U43">
+        <v>8</v>
+      </c>
+      <c r="V43">
+        <v>7</v>
+      </c>
+      <c r="W43">
         <v>6</v>
-      </c>
-      <c r="V43">
-        <v>7</v>
-      </c>
-      <c r="W43">
-        <v>5</v>
       </c>
       <c r="X43">
         <v>5</v>
       </c>
       <c r="Y43">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3893,19 +3878,19 @@
         <v>-1</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -3929,7 +3914,7 @@
         <v>10</v>
       </c>
       <c r="U44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V44">
         <v>9</v>
@@ -3970,19 +3955,19 @@
         <v>-1</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4012,7 +3997,7 @@
         <v>10</v>
       </c>
       <c r="W45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X45">
         <v>10</v>
@@ -4160,7 +4145,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -4169,7 +4154,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -4178,7 +4163,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4187,7 +4172,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4219,7 +4204,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -4237,7 +4222,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4278,16 +4263,16 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L6">
         <v>100</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -4296,16 +4281,16 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4396,7 +4381,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -4414,7 +4399,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4455,7 +4440,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -4473,7 +4458,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4806,10 +4791,10 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J15">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K15">
         <v>94.3</v>
@@ -4824,10 +4809,10 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P15">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q15">
         <v>94.3</v>
@@ -4865,13 +4850,13 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K16">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4883,13 +4868,13 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P16">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q16">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -5160,7 +5145,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J21">
         <v>100</v>
@@ -5178,7 +5163,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -5281,16 +5266,16 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -5299,16 +5284,16 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5337,7 +5322,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -5355,7 +5340,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5517,16 +5502,16 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N27">
         <v>100</v>
@@ -5535,16 +5520,16 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5632,10 +5617,10 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -5650,10 +5635,10 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5691,10 +5676,10 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -5709,10 +5694,10 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P30">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5986,13 +5971,13 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J35">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="L35">
         <v>100</v>
@@ -6004,13 +5989,13 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q35">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -6104,37 +6089,37 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J37">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L37">
         <v>100</v>
       </c>
       <c r="M37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N37">
         <v>100</v>
       </c>
       <c r="O37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P37">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q37">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R37">
         <v>100</v>
       </c>
       <c r="S37">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6225,16 +6210,16 @@
         <v>100</v>
       </c>
       <c r="J39">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="L39">
         <v>100</v>
       </c>
       <c r="M39">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N39">
         <v>100</v>
@@ -6243,16 +6228,16 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q39">
-        <v>100</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R39">
         <v>100</v>
       </c>
       <c r="S39">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6402,16 +6387,16 @@
         <v>100</v>
       </c>
       <c r="J42">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K42">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="L42">
         <v>100</v>
       </c>
       <c r="M42">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N42">
         <v>100</v>
@@ -6420,16 +6405,16 @@
         <v>100</v>
       </c>
       <c r="P42">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q42">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="R42">
         <v>100</v>
       </c>
       <c r="S42">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6461,7 +6446,7 @@
         <v>100</v>
       </c>
       <c r="J43">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K43">
         <v>100</v>
@@ -6479,7 +6464,7 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q43">
         <v>100</v>
@@ -6520,7 +6505,7 @@
         <v>100</v>
       </c>
       <c r="J44">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K44">
         <v>100</v>
@@ -6538,7 +6523,7 @@
         <v>100</v>
       </c>
       <c r="P44">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q44">
         <v>100</v>
@@ -6663,7 +6648,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -6672,19 +6657,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>81</v>
+        <v>85.7</v>
       </c>
       <c r="G2" s="2">
-        <v>19</v>
+        <v>14.3</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6695,7 +6680,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -6704,16 +6689,16 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2">
-        <v>83.3</v>
+        <v>90.5</v>
       </c>
       <c r="G3" s="2">
-        <v>16.7</v>
+        <v>9.5</v>
       </c>
       <c r="H3">
         <v>7.9</v>
@@ -6736,19 +6721,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>90.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>9.5</v>
+        <v>7.1</v>
       </c>
       <c r="H4">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6759,7 +6744,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -6780,7 +6765,7 @@
         <v>7.1</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6794,25 +6779,25 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6">
         <v>42</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="G6" s="2">
-        <v>7.1</v>
+        <v>4.8</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6894,7 +6879,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6932,16 +6917,16 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6955,16 +6940,16 @@
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6972,19 +6957,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920105</v>
+        <v>22330051920108</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
         <v>67</v>
@@ -6995,22 +6980,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920105</v>
+        <v>22330051920108</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7018,19 +7003,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920116</v>
+        <v>22330051920114</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
@@ -7044,13 +7029,13 @@
         <v>22330051920116</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -7067,113 +7052,21 @@
         <v>22330051920122</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>66</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920122</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="D9" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920097</v>
-      </c>
-      <c r="B10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920088</v>
-      </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920121</v>
-      </c>
-      <c r="B12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCM - Estadisticos 20231.xlsx
+++ b/grupos/3ALCM - Estadisticos 20231.xlsx
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>8</v>
@@ -831,7 +831,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>9</v>
@@ -949,7 +949,7 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>7</v>
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1062,7 +1062,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>9</v>
@@ -1103,7 +1103,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>7</v>
@@ -1180,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -1216,7 +1216,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1257,7 +1257,7 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>10</v>
@@ -1334,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>8</v>
@@ -1370,7 +1370,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1411,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -1447,7 +1447,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>9</v>
@@ -1488,7 +1488,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>8</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>8</v>
@@ -1601,7 +1601,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1642,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -1719,7 +1719,7 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>7</v>
@@ -1796,7 +1796,7 @@
         <v>8</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
         <v>9</v>
@@ -1832,7 +1832,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -1873,7 +1873,7 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -1909,7 +1909,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
         <v>9</v>
@@ -1950,7 +1950,7 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>5</v>
@@ -2027,7 +2027,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>9</v>
@@ -2063,7 +2063,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2104,7 +2104,7 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>7</v>
@@ -2140,7 +2140,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2181,7 +2181,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>10</v>
@@ -2258,7 +2258,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I23">
         <v>5</v>
@@ -2335,7 +2335,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2412,7 +2412,7 @@
         <v>10</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>8</v>
@@ -2489,7 +2489,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>9</v>
@@ -2525,7 +2525,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2566,7 +2566,7 @@
         <v>5</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I27">
         <v>5</v>
@@ -2602,7 +2602,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>5</v>
@@ -2643,7 +2643,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -2720,7 +2720,7 @@
         <v>8</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>9</v>
@@ -2756,7 +2756,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
         <v>8</v>
@@ -2797,7 +2797,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>6</v>
@@ -2874,7 +2874,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -2951,7 +2951,7 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -2987,7 +2987,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>9</v>
@@ -3028,7 +3028,7 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -3064,7 +3064,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
         <v>9</v>
@@ -3105,7 +3105,7 @@
         <v>8</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
         <v>7</v>
@@ -3182,7 +3182,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
         <v>8</v>
@@ -3259,7 +3259,7 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
         <v>9</v>
@@ -3336,7 +3336,7 @@
         <v>5</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I37">
         <v>7</v>
@@ -3413,7 +3413,7 @@
         <v>10</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>9</v>
@@ -3490,7 +3490,7 @@
         <v>9</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
         <v>10</v>
@@ -3567,7 +3567,7 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
         <v>8</v>
@@ -3644,7 +3644,7 @@
         <v>10</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
         <v>8</v>
@@ -3721,7 +3721,7 @@
         <v>8</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I42">
         <v>8</v>
@@ -3757,7 +3757,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U42">
         <v>7</v>
@@ -3798,7 +3798,7 @@
         <v>8</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I43">
         <v>9</v>
@@ -3834,7 +3834,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U43">
         <v>8</v>
@@ -3875,7 +3875,7 @@
         <v>9</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I44">
         <v>9</v>
@@ -3952,7 +3952,7 @@
         <v>10</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I45">
         <v>9</v>
@@ -6829,7 +6829,7 @@
         <v>2.4</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ALCM - Estadisticos 20231.xlsx
+++ b/grupos/3ALCM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -218,18 +218,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
+    <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
@@ -245,49 +245,31 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
+    <t>LUGO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SOTO</t>
-  </si>
-  <si>
-    <t>GIL</t>
+    <t>ZAYRA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
   </si>
   <si>
     <t>ANETTE</t>
-  </si>
-  <si>
-    <t>BARUCH BOSET</t>
-  </si>
-  <si>
-    <t>ILEANA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JESUS</t>
   </si>
 </sst>
 </file>
@@ -813,25 +795,25 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -840,10 +822,10 @@
         <v>8</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -890,22 +872,22 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -967,22 +949,22 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -991,7 +973,7 @@
         <v>7</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W6">
         <v>7</v>
@@ -1044,40 +1026,40 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>9</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>7</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1121,31 +1103,31 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1198,31 +1180,31 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1275,28 +1257,28 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>10</v>
@@ -1352,22 +1334,22 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1379,7 +1361,7 @@
         <v>9</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1429,37 +1411,37 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
         <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1506,28 +1488,28 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>10</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1583,28 +1565,28 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1660,37 +1642,37 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
       </c>
       <c r="U15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>8</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1737,22 +1719,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1761,7 +1743,7 @@
         <v>7</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1770,7 +1752,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1814,28 +1796,28 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -1891,34 +1873,34 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -1968,25 +1950,25 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>5</v>
@@ -1995,13 +1977,13 @@
         <v>8</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2045,28 +2027,28 @@
         <v>9</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2122,40 +2104,40 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>9</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2199,34 +2181,34 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>9</v>
@@ -2276,40 +2258,40 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>5</v>
       </c>
       <c r="V23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2353,28 +2335,28 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>10</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2386,7 +2368,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2430,22 +2412,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2507,31 +2489,31 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2584,22 +2566,22 @@
         <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2608,16 +2590,16 @@
         <v>5</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2661,22 +2643,22 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2738,34 +2720,34 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>8</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -2815,34 +2797,34 @@
         <v>7</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>8</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30">
         <v>7</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -2892,22 +2874,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2922,7 +2904,7 @@
         <v>9</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2969,28 +2951,28 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>10</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -3002,7 +2984,7 @@
         <v>9</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3046,28 +3028,28 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>10</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3079,7 +3061,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3123,22 +3105,22 @@
         <v>10</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3150,10 +3132,10 @@
         <v>9</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>9</v>
@@ -3200,37 +3182,37 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>9</v>
       </c>
       <c r="U35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y35">
         <v>7</v>
@@ -3277,28 +3259,28 @@
         <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>9</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>10</v>
@@ -3307,7 +3289,7 @@
         <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3354,28 +3336,28 @@
         <v>6</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T37">
         <v>7</v>
       </c>
       <c r="U37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3387,7 +3369,7 @@
         <v>7</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3431,22 +3413,22 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3508,28 +3490,28 @@
         <v>8</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
         <v>10</v>
       </c>
       <c r="U39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V39">
         <v>9</v>
@@ -3538,7 +3520,7 @@
         <v>8</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>9</v>
@@ -3585,22 +3567,22 @@
         <v>9</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -3662,22 +3644,22 @@
         <v>10</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -3739,22 +3721,22 @@
         <v>7</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T42">
         <v>10</v>
@@ -3766,10 +3748,10 @@
         <v>7</v>
       </c>
       <c r="W42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y42">
         <v>8</v>
@@ -3816,37 +3798,37 @@
         <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T43">
         <v>9</v>
       </c>
       <c r="U43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V43">
         <v>7</v>
       </c>
       <c r="W43">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y43">
         <v>9</v>
@@ -3893,40 +3875,40 @@
         <v>9</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T44">
         <v>10</v>
       </c>
       <c r="U44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V44">
         <v>9</v>
       </c>
       <c r="W44">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X44">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y44">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -3970,22 +3952,22 @@
         <v>10</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T45">
         <v>10</v>
@@ -4163,7 +4145,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q4">
         <v>100</v>
@@ -4172,7 +4154,7 @@
         <v>100</v>
       </c>
       <c r="S4">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4222,7 +4204,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -4281,16 +4263,16 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Q6">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R6">
         <v>100</v>
       </c>
       <c r="S6">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4340,10 +4322,10 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4399,10 +4381,10 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -4458,7 +4440,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4756,7 +4738,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -4809,13 +4791,13 @@
         <v>100</v>
       </c>
       <c r="O15">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="P15">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="Q15">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4868,13 +4850,13 @@
         <v>100</v>
       </c>
       <c r="O16">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="P16">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="Q16">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4989,7 +4971,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -5048,10 +5030,10 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -5163,7 +5145,7 @@
         <v>100</v>
       </c>
       <c r="O21">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="P21">
         <v>100</v>
@@ -5225,10 +5207,10 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -5284,16 +5266,16 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>76</v>
+        <v>83.8</v>
       </c>
       <c r="Q23">
-        <v>91.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5340,7 +5322,7 @@
         <v>100</v>
       </c>
       <c r="O24">
-        <v>97.5</v>
+        <v>81.7</v>
       </c>
       <c r="P24">
         <v>100</v>
@@ -5520,16 +5502,16 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="Q27">
-        <v>94.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5635,13 +5617,13 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>95</v>
+        <v>88.3</v>
       </c>
       <c r="P29">
-        <v>98</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -5694,13 +5676,13 @@
         <v>100</v>
       </c>
       <c r="O30">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="P30">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -5989,19 +5971,19 @@
         <v>100</v>
       </c>
       <c r="O35">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="P35">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="Q35">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="R35">
         <v>100</v>
       </c>
       <c r="S35">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -6107,19 +6089,19 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>95</v>
+        <v>88.3</v>
       </c>
       <c r="P37">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Q37">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="R37">
         <v>100</v>
       </c>
       <c r="S37">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6228,16 +6210,16 @@
         <v>100</v>
       </c>
       <c r="P39">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="Q39">
-        <v>91.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R39">
         <v>100</v>
       </c>
       <c r="S39">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6405,16 +6387,16 @@
         <v>100</v>
       </c>
       <c r="P42">
-        <v>95</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="Q42">
-        <v>97.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="R42">
         <v>100</v>
       </c>
       <c r="S42">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6464,10 +6446,10 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Q43">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="R43">
         <v>100</v>
@@ -6523,10 +6505,10 @@
         <v>100</v>
       </c>
       <c r="P44">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="Q44">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="R44">
         <v>100</v>
@@ -6648,7 +6630,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -6657,19 +6639,19 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>85.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>14.3</v>
+        <v>7.1</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6680,7 +6662,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -6689,19 +6671,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>90.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>9.5</v>
+        <v>2.4</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6712,7 +6694,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -6721,19 +6703,19 @@
         <v>42</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>92.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>7.1</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6744,7 +6726,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -6753,19 +6735,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>92.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6776,28 +6758,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6">
         <v>42</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6808,28 +6790,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C7">
         <v>42</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6879,7 +6861,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6911,22 +6893,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920098</v>
+        <v>22330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6934,22 +6916,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920098</v>
+        <v>22330051920100</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6957,22 +6939,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920108</v>
+        <v>22330051920105</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6980,22 +6962,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920108</v>
+        <v>22330051920105</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7003,70 +6985,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920114</v>
+        <v>22330051920098</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>66</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920116</v>
-      </c>
-      <c r="B7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>68</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920122</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" t="s">
-        <v>89</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ALCM - Estadisticos 20231.xlsx
+++ b/grupos/3ALCM - Estadisticos 20231.xlsx
@@ -813,22 +813,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -890,22 +890,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -970,19 +970,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1044,22 +1044,22 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1121,22 +1121,22 @@
         <v>9</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1198,22 +1198,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1278,16 +1278,16 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1355,19 +1355,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1429,22 +1429,22 @@
         <v>9</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1509,19 +1509,19 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1586,19 +1586,19 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1660,22 +1660,22 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1740,19 +1740,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1814,22 +1814,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1891,22 +1891,22 @@
         <v>7</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1968,22 +1968,22 @@
         <v>5</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>5</v>
       </c>
       <c r="V19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2048,19 +2048,19 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2122,22 +2122,22 @@
         <v>6</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2199,22 +2199,22 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2276,22 +2276,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>5</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2356,19 +2356,19 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2433,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2510,19 +2510,19 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2584,22 +2584,22 @@
         <v>9</v>
       </c>
       <c r="T27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>5</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>5</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2664,10 +2664,10 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2676,7 +2676,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2738,22 +2738,22 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2815,22 +2815,22 @@
         <v>6</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2895,16 +2895,16 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>10</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2972,19 +2972,19 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3049,19 +3049,19 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3126,19 +3126,19 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3200,22 +3200,22 @@
         <v>7</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X35">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3277,22 +3277,22 @@
         <v>10</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>10</v>
       </c>
       <c r="W36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y36">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3354,22 +3354,22 @@
         <v>7</v>
       </c>
       <c r="T37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V37">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3511,19 +3511,19 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W39">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3588,19 +3588,19 @@
         <v>10</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V41">
         <v>10</v>
@@ -3742,19 +3742,19 @@
         <v>10</v>
       </c>
       <c r="U42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W42">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y42">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3816,22 +3816,22 @@
         <v>10</v>
       </c>
       <c r="T43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X43">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y43">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3896,19 +3896,19 @@
         <v>10</v>
       </c>
       <c r="U44">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X44">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y44">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -6651,7 +6651,7 @@
         <v>7.1</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>2.4</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6715,7 +6715,7 @@
         <v>2.4</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3ALCM - Estadisticos 20231.xlsx
+++ b/grupos/3ALCM - Estadisticos 20231.xlsx
@@ -813,22 +813,22 @@
         <v>9</v>
       </c>
       <c r="T4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -890,22 +890,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -970,19 +970,19 @@
         <v>10</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1044,22 +1044,22 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1121,22 +1121,22 @@
         <v>9</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1198,22 +1198,22 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1278,16 +1278,16 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1355,19 +1355,19 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1429,22 +1429,22 @@
         <v>9</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1509,19 +1509,19 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1586,19 +1586,19 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1660,22 +1660,22 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1740,19 +1740,19 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1814,22 +1814,22 @@
         <v>9</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1891,22 +1891,22 @@
         <v>7</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1968,22 +1968,22 @@
         <v>5</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>5</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2048,19 +2048,19 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2122,22 +2122,22 @@
         <v>6</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2199,22 +2199,22 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2276,22 +2276,22 @@
         <v>8</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>5</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X23">
         <v>5</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2356,19 +2356,19 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2433,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2510,19 +2510,19 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2584,22 +2584,22 @@
         <v>9</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U27">
         <v>5</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>5</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2664,10 +2664,10 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -2676,7 +2676,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2738,22 +2738,22 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2815,22 +2815,22 @@
         <v>6</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2895,16 +2895,16 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>10</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>10</v>
@@ -2972,19 +2972,19 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3049,19 +3049,19 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3126,19 +3126,19 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y34">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3200,22 +3200,22 @@
         <v>7</v>
       </c>
       <c r="T35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X35">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y35">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3277,22 +3277,22 @@
         <v>10</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V36">
         <v>10</v>
       </c>
       <c r="W36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3354,22 +3354,22 @@
         <v>7</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y37">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3511,19 +3511,19 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W39">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y39">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3588,19 +3588,19 @@
         <v>10</v>
       </c>
       <c r="U40">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y40">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3665,7 +3665,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>10</v>
@@ -3742,19 +3742,19 @@
         <v>10</v>
       </c>
       <c r="U42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y42">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3816,22 +3816,22 @@
         <v>10</v>
       </c>
       <c r="T43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y43">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -3896,19 +3896,19 @@
         <v>10</v>
       </c>
       <c r="U44">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X44">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y44">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -6651,7 +6651,7 @@
         <v>7.1</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6683,7 +6683,7 @@
         <v>2.4</v>
       </c>
       <c r="H3">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6715,7 +6715,7 @@
         <v>2.4</v>
       </c>
       <c r="H4">
-        <v>9.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6779,7 +6779,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
